--- a/referee_response/time_to_departure/table3_conflicted_halves_fye1.xlsx
+++ b/referee_response/time_to_departure/table3_conflicted_halves_fye1.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -471,14 +471,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table III with Conflicted CIO Split Into the First and Second Half of Tenure: Fiscal-Year-End Fixed Effects and CIO Fixed Effects</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="182" customHeight="1">
+          <t>Table III with Conflicted CIO Split Into the First and Second Half of Tenure: Fiscal-Year-End Fixed Effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="168" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This table repeats columns 2-4 of Table III with fiscal-year-end date fixed effects in place of year fixed effects, and adds CIO fixed effects (column 4), with Conflicted CIO split into two indicators: Conflicted CIO x First Half of Tenure equals 1 in a conflicted CIO's plan-years in which tenure at the plan is at most half of tenure at departure, and Conflicted CIO x Second Half of Tenure equals 1 in the remaining conflicted plan-years (195 and 164 plan-years in the Table III sample). The reference group is the non-conflicted plan-years. The performance measure in Panel A is Peer-Adjusted Return; in Panel B it is Benchmark-Adjusted Return (plan return minus its policy benchmark: reported, else inferred grade A or B). CIO fixed effects are for each CIO's tenure at a plan. Because Conflicted CIO is constant within a CIO's tenure (it is 0 only in the departure year), column 4 identifies only the difference between the two halves within the same CIO, reported as 'Second minus first half'; Financial Center, CIO Prior Private Experience and CIO Attended Elite College do not vary within a CIO's tenure and are absorbed; column 4 uses the same plan-years as columns 1-3. 'Second minus first half' is the difference between the two half coefficients, with its p-value. Other variables are as defined in Table I. t-statistics in parentheses; standard errors double clustered by plan and year. ***, **, and * denote significance at the 1%, 5%, and 10% level.</t>
+          <t>This table repeats columns 2-4 of Table III with fiscal-year-end date fixed effects in place of year fixed effects, with Conflicted CIO split into two indicators: Conflicted CIO x First Half of Tenure equals 1 in a conflicted CIO's plan-years in which tenure at the plan is at most half of tenure at departure, and Conflicted CIO x Second Half of Tenure equals 1 in the remaining conflicted plan-years (195 and 164 plan-years in the Table III sample). In columns 1-3 the reference group is the non-conflicted plan-years. Column 4 uses only conflicted CIOs' plan-years and adds CIO fixed effects, so First Half is the reference and the Second Half coefficient is the within-CIO change from the first to the second half. The performance measure in Panel A is Peer-Adjusted Return; in Panel B it is Benchmark-Adjusted Return (plan return minus its policy benchmark: reported, else inferred grade A or B). CIO fixed effects are for each CIO's tenure at a plan; Financial Center, CIO Prior Private Experience and CIO Attended Elite College do not vary within a CIO's tenure and are absorbed. 'Second minus first half' is the difference between the two half coefficients, with its p-value. Other variables are as defined in Table I. t-statistics in parentheses; standard errors double clustered by plan and year. ***, **, and * denote significance at the 1%, 5%, and 10% level.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
@@ -600,9 +600,9 @@
           <t>-0.633*</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>-0.791</t>
         </is>
       </c>
     </row>
@@ -622,6 +622,11 @@
           <t>(-2.01)</t>
         </is>
       </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>(-1.33)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -646,7 +651,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>0.037</t>
         </is>
       </c>
     </row>
@@ -668,7 +673,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>(-0.37)</t>
+          <t>(0.27)</t>
         </is>
       </c>
     </row>
@@ -695,7 +700,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>-3.654**</t>
+          <t>1.041</t>
         </is>
       </c>
     </row>
@@ -717,7 +722,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>(-2.36)</t>
+          <t>(0.68)</t>
         </is>
       </c>
     </row>
@@ -744,7 +749,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>-0.045**</t>
+          <t>-0.063**</t>
         </is>
       </c>
     </row>
@@ -766,7 +771,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>(-2.75)</t>
+          <t>(-2.13)</t>
         </is>
       </c>
     </row>
@@ -793,7 +798,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-1.455***</t>
         </is>
       </c>
     </row>
@@ -815,7 +820,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>(0.16)</t>
+          <t>(-3.18)</t>
         </is>
       </c>
     </row>
@@ -842,7 +847,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-1.542***</t>
         </is>
       </c>
     </row>
@@ -864,7 +869,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>(0.10)</t>
+          <t>(-3.26)</t>
         </is>
       </c>
     </row>
@@ -891,7 +896,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>-0.081</t>
+          <t>-1.724**</t>
         </is>
       </c>
     </row>
@@ -913,7 +918,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>(-0.71)</t>
+          <t>(-2.65)</t>
         </is>
       </c>
     </row>
@@ -940,7 +945,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>-1.380***</t>
         </is>
       </c>
     </row>
@@ -962,7 +967,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>(0.58)</t>
+          <t>(-3.12)</t>
         </is>
       </c>
     </row>
@@ -989,7 +994,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-1.500***</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1016,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>(0.12)</t>
+          <t>(-3.11)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1043,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-1.316</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1065,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>(-0.10)</t>
+          <t>(-1.18)</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1092,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>-0.122</t>
+          <t>-1.344***</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>(-1.06)</t>
+          <t>(-3.02)</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1141,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-1.336**</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1163,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>(0.24)</t>
+          <t>(-2.78)</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1209,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>-0.545</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1231,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>(1.34)</t>
+          <t>(-0.23)</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1258,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>-0.204</t>
+          <t>-0.053</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1280,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>(-1.06)</t>
+          <t>(-0.13)</t>
         </is>
       </c>
     </row>
@@ -1378,11 +1383,6 @@
           <t>0.248</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>-0.866</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
@@ -1400,11 +1400,6 @@
           <t>(0.27)</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>(-1.27)</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -1429,7 +1424,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>9.058</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1446,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>(0.13)</t>
+          <t>(1.29)</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1473,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>-0.791</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1500,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>(1.08)</t>
+          <t>(-1.33)</t>
         </is>
       </c>
     </row>
@@ -1532,1329 +1527,1378 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.200</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Observations</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>1,478</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>1,482</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>1,477</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>1,358</t>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Conflicted CIOs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>Adjusted R-squared</t>
+          <t>Observations</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>1,478</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1,482</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1,477</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>263</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>Plan FE</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Adjusted R-squared</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>0.070</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>0.081</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>0.089</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>0.023</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
+          <t>Plan FE</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
           <t>CIO FE</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Fiscal-year-end FE</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>Panel B. Benchmark-Adjusted Return</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>Conflicted CIO x First Half of Tenure (0/1)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>-0.574***</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>-0.574**</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>-0.619**</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>(-3.29)</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>(-2.55)</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>(-2.77)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Conflicted CIO x Second Half of Tenure (0/1)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>-0.356**</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>-0.206</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="9" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>(-2.23)</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>(-1.04)</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>(-0.81)</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>(0.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Investment Return (t-1)</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>0.037</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>0.006</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>0.020</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>-0.185*</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>(0.53)</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>(0.33)</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>(0.33)</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>(-1.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Log (Plan Size) (t-1)</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>-1.138*</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>-0.037</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>0.583</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>(0.06)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>(-1.82)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>(-0.06)</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>(0.76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Funding Ratio (t-1)</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>(0.91)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>(-1.52)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>(-1.62)</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>(-0.43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Equity Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>-0.008</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>-0.002</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>(0.53)</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>(0.33)</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>(0.33)</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>(-0.04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Log (Plan Size) (t-1)</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>-1.138*</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>-0.037</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>-0.963</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>-0.727</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>(-0.07)</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>(-0.01)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>(0.14)</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>(-1.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Fixed Income Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>-0.018</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>-0.721</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>(-0.09)</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>(-0.10)</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>(0.07)</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>(-1.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Real Estate Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>-0.029</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>-0.048</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>-0.817</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>(-0.29)</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>(-0.27)</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>(-0.25)</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>(-1.62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Private Equity Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>-0.727</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>(0.06)</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>(-1.82)</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>(-0.12)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>(0.18)</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>(-1.70)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Hedge Fund Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>-0.710</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>(0.01)</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>(-0.03)</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>(0.10)</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>(-1.56)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Misc. Alternatives Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>-0.023</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>0.027</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>-0.130</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>(-0.15)</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>(-0.13)</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>(0.15)</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>(-0.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Commodities Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>-0.032</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>-0.524</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>(-0.25)</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>(-0.18)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>(-0.06)</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>(-0.98)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>Funding Ratio (t-1)</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>(-1.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Cash Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>0.038</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>-0.588</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>(0.09)</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>(0.19)</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>(0.23)</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>(-1.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Financial Center (0/1)</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>-0.189*</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>(-2.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Log (CIO Age) (t-1)</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>-1.145**</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>-0.139</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>0.071</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>2.179*</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>(-2.28)</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>(-0.20)</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>(0.08)</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>(1.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Log (CIO Tenure) (t-1)</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>-0.075</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>-0.196</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>-0.540**</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>(-0.09)</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>(-0.64)</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>(-1.43)</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>(-2.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>CIO Prior Private Experience (0/1)</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>0.096</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>0.138</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>(0.70)</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>(0.70)</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>(0.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>CIO Attended Elite College (0/1)</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>-0.192</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>0.091</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>-0.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>(-1.11)</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>(0.46)</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>(-0.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Separate Investment Board (0/1)</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>0.281</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>0.724</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>(1.71)</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>(-0.06)</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>(1.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>% Political Appointees on Board</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>-0.017</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>(0.91)</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>(-1.52)</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>(-1.62)</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>(-1.48)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>Equity Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>-0.008</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>-0.002</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>0.086</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>(-0.07)</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>(-0.01)</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>(0.14)</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>(0.45)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>Fixed Income Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>-0.011</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>-0.018</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>0.012</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>0.082</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>(-0.09)</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>0.390</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>-0.244</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>20.753***</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>(-0.10)</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>(0.07)</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>(0.43)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Real Estate Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>-0.029</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>-0.048</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>0.009</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>(-0.29)</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>(-0.27)</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>(-0.25)</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>(0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Private Equity Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>0.007</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>-0.021</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>0.126</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>(0.06)</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>(-0.12)</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>(0.18)</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>(0.66)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Hedge Fund Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>0.016</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>0.104</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>(0.01)</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>(-0.03)</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>(0.10)</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>(0.53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Misc. Alternatives Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>-0.016</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>-0.023</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>0.085</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>(-0.15)</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>(-0.13)</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>(0.15)</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>(0.43)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>Commodities Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>-0.032</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>-0.011</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>(-0.25)</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>(0.24)</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>(-0.18)</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>(-0.06)</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>(0.02)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Cash Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>0.011</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>0.038</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>(0.09)</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>(0.19)</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>(0.23)</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>(0.55)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>Financial Center (0/1)</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>-0.189*</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>(-2.09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Log (CIO Age) (t-1)</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>-1.145**</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>-0.139</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>0.071</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>-0.835</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>(-2.28)</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>(-0.20)</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>(0.08)</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>(-0.78)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>Log (CIO Tenure) (t-1)</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>-0.011</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>-0.075</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>-0.196</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>-0.220</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>(-0.09)</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>(-0.64)</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>(-1.43)</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>(-1.09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>CIO Prior Private Experience (0/1)</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>0.096</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>0.138</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>0.072</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>(0.70)</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>(0.70)</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>(0.34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>CIO Attended Elite College (0/1)</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>-0.192</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>0.091</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>-0.007</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>(-1.11)</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>(0.46)</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>(-0.03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>Separate Investment Board (0/1)</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>0.281</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>-0.057</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>0.724</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>-0.304</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>(1.71)</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>(-0.06)</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>(1.22)</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>(-0.51)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>% Political Appointees on Board</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>0.390</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>-0.244</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>2.096</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>(-0.10)</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>(0.24)</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>(-0.18)</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>(1.34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>(5.43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>Second minus first half</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>0.217</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>0.367</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>0.449*</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>0.649**</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  t-statistic</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>(1.06)</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>(1.42)</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>(1.91)</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>(2.83)</t>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>0.046</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  t-statistic</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>(1.06)</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>(1.42)</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>(1.91)</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>(0.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  p-value</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>0.304</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>0.173</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>0.011</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>Observations</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>1,313</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>1,319</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>1,312</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>1,207</t>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>0.908</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>Adjusted R-squared</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
-      </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>0.143</t>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Conflicted CIOs</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>Plan FE</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Observations</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>1,313</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>1,319</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>1,312</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>244</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
+          <t>Adjusted R-squared</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>0.167</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>0.450</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>Plan FE</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
           <t>CIO FE</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
+      <c r="C110" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D108" s="12" t="inlineStr">
+      <c r="D110" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="13" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="13" t="inlineStr">
         <is>
           <t>Fiscal-year-end FE</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2875,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2892,10 +2936,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="196" customHeight="1">
+    <row r="2" ht="182" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This table repeats columns 2-4 of Table III with fiscal-year-end date fixed effects in place of year fixed effects, and adds CIO fixed effects (column 4), with Conflicted CIO split into two indicators: Conflicted CIO x First Half of Tenure equals 1 in a conflicted CIO's plan-years in which tenure at the plan is at most half of tenure at departure, and Conflicted CIO x Second Half of Tenure equals 1 in the remaining conflicted plan-years (195 and 164 plan-years in the Table III sample). The reference group is the non-conflicted plan-years. The performance measure in Panel A is Peer-Adjusted Return; in Panel B it is Benchmark-Adjusted Return (plan return minus its policy benchmark: reported, else inferred grade A or B). CIO fixed effects are for each CIO's tenure at a plan. Because Conflicted CIO is constant within a CIO's tenure (it is 0 only in the departure year), column 4 identifies only the difference between the two halves within the same CIO, reported as 'Second minus first half'; Financial Center, CIO Prior Private Experience and CIO Attended Elite College do not vary within a CIO's tenure and are absorbed; column 4 uses the same plan-years as columns 1-3. 'Second minus first half' is the difference between the two half coefficients, with its p-value. Other variables are as defined in Table I. t-statistics in parentheses; standard errors double clustered by plan and year. ***, **, and * denote significance at the 1%, 5%, and 10% level. Log (CIO Tenure) and Log (CIO Age) are dropped from the controls because tenure rises mechanically from the first to the second half.</t>
+          <t>This table repeats columns 2-4 of Table III with fiscal-year-end date fixed effects in place of year fixed effects, with Conflicted CIO split into two indicators: Conflicted CIO x First Half of Tenure equals 1 in a conflicted CIO's plan-years in which tenure at the plan is at most half of tenure at departure, and Conflicted CIO x Second Half of Tenure equals 1 in the remaining conflicted plan-years (195 and 164 plan-years in the Table III sample). In columns 1-3 the reference group is the non-conflicted plan-years. Column 4 uses only conflicted CIOs' plan-years and adds CIO fixed effects, so First Half is the reference and the Second Half coefficient is the within-CIO change from the first to the second half. The performance measure in Panel A is Peer-Adjusted Return; in Panel B it is Benchmark-Adjusted Return (plan return minus its policy benchmark: reported, else inferred grade A or B). CIO fixed effects are for each CIO's tenure at a plan; Financial Center, CIO Prior Private Experience and CIO Attended Elite College do not vary within a CIO's tenure and are absorbed. 'Second minus first half' is the difference between the two half coefficients, with its p-value. Other variables are as defined in Table I. t-statistics in parentheses; standard errors double clustered by plan and year. ***, **, and * denote significance at the 1%, 5%, and 10% level. Log (CIO Tenure) and Log (CIO Age) are dropped from the controls because tenure rises mechanically from the first to the second half.</t>
         </is>
       </c>
     </row>
@@ -2975,7 +3019,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reference</t>
         </is>
       </c>
     </row>
@@ -3017,9 +3061,9 @@
           <t>-0.783**</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>-0.780</t>
         </is>
       </c>
     </row>
@@ -3039,6 +3083,11 @@
           <t>(-2.31)</t>
         </is>
       </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>(-1.42)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -3063,7 +3112,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>0.032</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3134,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>(-0.15)</t>
+          <t>(0.24)</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3161,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>-3.689**</t>
+          <t>1.030</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3183,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>(-2.47)</t>
+          <t>(0.68)</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3210,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>-0.046***</t>
+          <t>-0.063**</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3232,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>(-3.13)</t>
+          <t>(-2.54)</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3259,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-1.469***</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3281,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>(0.24)</t>
+          <t>(-3.26)</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3308,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-1.557***</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3330,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>(0.14)</t>
+          <t>(-3.35)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3357,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>-0.071</t>
+          <t>-1.740**</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3379,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>(-0.61)</t>
+          <t>(-2.70)</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3406,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>-1.396***</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3428,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>(0.33)</t>
+          <t>(-3.22)</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3455,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-1.514***</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3477,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>(0.22)</t>
+          <t>(-3.21)</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3504,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-1.344</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3526,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>(-0.12)</t>
+          <t>(-1.25)</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3553,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>-0.136</t>
+          <t>-1.362***</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3575,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>(-1.14)</t>
+          <t>(-3.12)</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3602,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>-1.351**</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3624,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>(0.28)</t>
+          <t>(-2.87)</t>
         </is>
       </c>
     </row>
@@ -3697,11 +3746,6 @@
           <t>0.106</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>-0.890</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
@@ -3719,11 +3763,6 @@
           <t>(0.12)</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>(-1.45)</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3748,7 +3787,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>7.710</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3809,7 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>(0.31)</t>
+          <t>(1.11)</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3836,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>0.290</t>
+          <t>-0.780</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3863,7 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>(1.06)</t>
+          <t>(-1.42)</t>
         </is>
       </c>
     </row>
@@ -3851,1231 +3890,1280 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.175</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>Observations</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>1,529</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>1,535</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>1,529</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>1,408</t>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Conflicted CIOs</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>Adjusted R-squared</t>
+          <t>Observations</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1,529</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>0.090</t>
+          <t>1,535</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1,529</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>263</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>Plan FE</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Adjusted R-squared</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>0.090</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>0.101</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>0.033</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
+          <t>Plan FE</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
           <t>CIO FE</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Fiscal-year-end FE</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>Panel B. Benchmark-Adjusted Return</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="n"/>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="n"/>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>Bench-adj. Ret. (t)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Conflicted CIO x First Half of Tenure (0/1)</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>-0.681***</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>-0.771***</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>-0.775***</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="9" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>(-2.94)</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>(-3.12)</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>(-3.14)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>Conflicted CIO x Second Half of Tenure (0/1)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>-0.307*</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>-0.344</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>-0.329</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="9" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>-0.142</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>(-1.76)</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>(-1.60)</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>(-1.42)</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>(-0.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Investment Return (t-1)</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>0.040</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>0.011</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>-0.013</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>-0.205**</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>(0.59)</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>(0.44)</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>(0.21)</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>(-2.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Log (Plan Size) (t-1)</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>-1.250*</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>-0.250</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>0.691</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>(-0.09)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>(-2.03)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>(-0.35)</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>(0.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Funding Ratio (t-1)</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>-0.020*</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>-0.015</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>(0.77)</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>(-1.83)</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>(-1.47)</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>(-0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Equity Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>-0.009</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>-0.726</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>(-0.20)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>(-0.05)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>(0.05)</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>(-1.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Fixed Income Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>-0.023</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>-0.002</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>-0.725</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>(-0.21)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>(-0.13)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>(-0.01)</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>(-1.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Real Estate Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>-0.064</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>-0.033</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>-0.779</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>(-0.62)</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>(-0.19)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>(-0.23)</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>(-1.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Private Equity Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>-0.008</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>-0.047</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>-0.761*</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>(-0.07)</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>(-0.27)</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>Log (Plan Size) (t-1)</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>-0.004</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>-1.250*</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>-1.080</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>(-0.09)</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>(-2.03)</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>(-0.35)</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>(-0.00)</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>(-1.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Hedge Fund Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>-0.008</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>-0.677</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>(-0.07)</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>(-0.06)</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>(0.03)</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>(-1.49)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Misc. Alternatives Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>-0.043</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>-0.047</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>-0.221</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>(-0.39)</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>(-0.26)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>(-0.04)</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>(-0.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Commodities Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>-0.077</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>-0.041</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>-0.033</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>-0.523</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>(-0.64)</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>(-0.22)</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>(-0.19)</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>(-1.09)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Funding Ratio (t-1)</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>-0.020*</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>-0.016</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>-0.021</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>(0.77)</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>(-1.83)</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>(-1.47)</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>(-1.54)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Equity Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>-0.022</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>-0.009</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>0.101</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>(-0.20)</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>(-0.05)</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Cash Allocation (t-1)</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>-0.607</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>(0.05)</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>(0.46)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>Fixed Income Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>-0.024</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>-0.023</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>-0.002</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>0.096</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>(-0.21)</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>(-0.13)</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>(-0.01)</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>(0.45)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>Real Estate Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>-0.064</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>-0.033</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>-0.036</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>0.048</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>(-0.62)</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>(-0.19)</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>(-0.23)</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>(0.24)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>Private Equity Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>-0.008</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>-0.047</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>0.115</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>(-0.07)</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>(-0.27)</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>(-0.00)</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>(0.53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Hedge Fund Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>-0.008</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>-0.011</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>0.118</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>(-0.07)</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>(-0.06)</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>(0.03)</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>(0.54)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Misc. Alternatives Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>-0.043</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>-0.047</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>(-0.39)</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>(-0.26)</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>(-0.04)</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>(0.33)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Commodities Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>-0.077</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>-0.041</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>-0.033</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>0.017</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>(-0.64)</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>(-0.22)</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>(-0.19)</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>(0.08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Cash Allocation (t-1)</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>0.130</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>(0.05)</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>(0.12)</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>(0.14)</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>(0.57)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>(-1.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>Financial Center (0/1)</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>-0.192*</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="9" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>(-1.84)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>CIO Prior Private Experience (0/1)</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>0.139</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>0.281</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>0.251</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="9" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>(1.52)</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>(1.39)</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
         <is>
           <t>(1.15)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>CIO Attended Elite College (0/1)</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>-0.190</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>0.029</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>-0.101</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="9" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>(-1.26)</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>(0.14)</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="D89" s="9" t="inlineStr">
         <is>
           <t>(-0.46)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>Separate Investment Board (0/1)</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>0.294*</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>-0.091</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>0.465</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>-0.443</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="9" t="inlineStr">
+    </row>
+    <row r="91">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>(1.76)</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>(-0.10)</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>(0.82)</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>(-0.83)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>% Political Appointees on Board</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>-0.114</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
         <is>
           <t>0.453</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
         <is>
           <t>-0.389</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>2.049</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="9" t="inlineStr">
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>21.665***</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>(-0.57)</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>(0.28)</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>(-0.28)</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>(1.29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>(7.41)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>Second minus first half</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>0.374*</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>0.427</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>0.446*</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>0.695***</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  t-statistic</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>(2.07)</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>(1.72)</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>(2.01)</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>(2.96)</t>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>-0.142</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  t-statistic</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>(2.07)</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>(1.72)</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>(2.01)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>(-0.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  p-value</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>0.053</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>0.102</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>0.059</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>Observations</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>1,353</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>1,361</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>1,353</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>1,245</t>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>0.739</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Adjusted R-squared</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>0.159</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>0.062</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>0.192</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>0.189</t>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Conflicted CIOs</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Plan FE</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Observations</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>1,353</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>1,361</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>1,353</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>244</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
+          <t>Adjusted R-squared</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>0.062</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>0.192</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>0.436</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>Plan FE</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
           <t>CIO FE</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C100" s="12" t="inlineStr">
+      <c r="C102" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D100" s="12" t="inlineStr">
+      <c r="D102" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E100" s="12" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="13" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Fiscal-year-end FE</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
